--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 00:54:33</t>
+          <t>2026-07-05 03:07:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 03:07:21</t>
+          <t>2026-07-05 05:20:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 05:20:02</t>
+          <t>2026-07-05 07:32:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 07:32:29</t>
+          <t>2026-07-05 09:44:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 09:44:07</t>
+          <t>2026-07-05 11:54:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 11:54:29</t>
+          <t>2026-07-05 14:04:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 14:04:08</t>
+          <t>2026-07-05 16:12:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 16:12:33</t>
+          <t>2026-07-05 18:20:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 18:20:14</t>
+          <t>2026-07-05 20:28:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -896,7 +896,7 @@
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
@@ -1022,19 +1022,19 @@
         <v>2.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5.4</v>
@@ -1046,13 +1046,13 @@
         <v>30</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>6.6</v>
@@ -1064,23 +1064,23 @@
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 20:28:02</t>
+          <t>2026-07-05 22:35:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,7 +878,7 @@
         <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
         <v>2.68</v>
@@ -887,7 +887,7 @@
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
@@ -902,7 +902,7 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
@@ -911,22 +911,22 @@
         <v>1.58</v>
       </c>
       <c r="X2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>12</v>
       </c>
-      <c r="Y2" t="n">
-        <v>11</v>
-      </c>
       <c r="Z2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>21</v>
@@ -935,10 +935,10 @@
         <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>30</v>
@@ -947,34 +947,34 @@
         <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
@@ -983,46 +983,46 @@
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC2" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7</v>
-      </c>
       <c r="BD2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF2" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2" t="n">
         <v>11.5</v>
@@ -1043,7 +1043,7 @@
         <v>4.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
         <v>7.6</v>
@@ -1080,7 +1080,261 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-05 22:35:32</t>
+          <t>2026-07-06 00:42:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-06 00:42:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -860,19 +860,19 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -887,7 +887,7 @@
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
@@ -896,19 +896,19 @@
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
@@ -938,7 +938,7 @@
         <v>18.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>30</v>
@@ -965,16 +965,16 @@
         <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
@@ -983,40 +983,40 @@
         <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>28</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 00:42:59</t>
+          <t>2026-07-06 02:50:15</t>
         </is>
       </c>
     </row>
@@ -1126,34 +1126,34 @@
         <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
         <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S3" t="n">
         <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
         <v>1.73</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
         <v>170</v>
@@ -1207,7 +1207,7 @@
         <v>970</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>230</v>
@@ -1219,16 +1219,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
         <v>3.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
@@ -1237,25 +1237,25 @@
         <v>4.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AY3" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC3" t="n">
         <v>6</v>
@@ -1264,13 +1264,13 @@
         <v>7.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BH3" t="n">
         <v>3.65</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 00:42:59</t>
+          <t>2026-07-06 02:50:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -905,7 +905,7 @@
         <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.59</v>
@@ -935,7 +935,7 @@
         <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -959,22 +959,22 @@
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AO2" t="n">
         <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
         <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
@@ -986,13 +986,13 @@
         <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ2" t="n">
         <v>7</v>
@@ -1007,16 +1007,16 @@
         <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1135,10 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.84</v>
@@ -1147,7 +1147,7 @@
         <v>1.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S3" t="n">
         <v>3.85</v>
@@ -1210,7 +1210,7 @@
         <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
         <v>970</v>
@@ -1228,7 +1228,7 @@
         <v>3.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AT3" t="n">
         <v>4</v>
@@ -1243,7 +1243,7 @@
         <v>2.12</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY3" t="n">
         <v>4.7</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 02:50:15</t>
+          <t>2026-07-06 04:57:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -872,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -920,7 +920,7 @@
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
@@ -944,7 +944,7 @@
         <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>55</v>
@@ -962,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="AO2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>4.9</v>
@@ -1010,7 +1010,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BF2" t="n">
         <v>8.199999999999999</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         <v>3.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
         <v>1.73</v>
@@ -1282,7 +1282,7 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 04:57:55</t>
+          <t>2026-07-06 07:05:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -860,7 +860,7 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
         <v>3.25</v>
@@ -872,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -887,13 +887,13 @@
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
         <v>5.2</v>
@@ -908,7 +908,7 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>1.59</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>10.5</v>
@@ -1129,19 +1129,19 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
@@ -1150,13 +1150,13 @@
         <v>1.3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.12</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI3" t="n">
         <v>170</v>
@@ -1219,61 +1219,61 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI3" t="n">
         <v>2.8</v>
@@ -1291,10 +1291,10 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
@@ -1312,7 +1312,7 @@
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 07:05:31</t>
+          <t>2026-07-06 09:13:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -872,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.49</v>
@@ -881,19 +881,19 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
         <v>5.2</v>
@@ -902,7 +902,7 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -1058,7 +1058,7 @@
         <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.47</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
         <v>7.4</v>
@@ -1162,7 +1162,7 @@
         <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
         <v>970</v>
@@ -1198,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ3" t="n">
         <v>970</v>
@@ -1234,7 +1234,7 @@
         <v>4.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV3" t="n">
         <v>5.7</v>
@@ -1276,65 +1276,65 @@
         <v>3.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 09:13:01</t>
+          <t>2026-07-06 11:20:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
         <v>2.66</v>
@@ -878,22 +878,22 @@
         <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
         <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
         <v>5.2</v>
@@ -902,7 +902,7 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -920,13 +920,13 @@
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>21</v>
@@ -938,13 +938,13 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
         <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
         <v>55</v>
@@ -953,70 +953,70 @@
         <v>44</v>
       </c>
       <c r="AL2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
         <v>11.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
         <v>28</v>
       </c>
       <c r="BC2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
         <v>1.58</v>
@@ -1129,10 +1129,10 @@
         <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>3.55</v>
@@ -1141,7 +1141,7 @@
         <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
         <v>1.94</v>
@@ -1159,16 +1159,16 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>2.72</v>
       </c>
       <c r="X3" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
         <v>95</v>
@@ -1177,7 +1177,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>970</v>
@@ -1189,22 +1189,22 @@
         <v>190</v>
       </c>
       <c r="AF3" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI3" t="n">
         <v>160</v>
       </c>
       <c r="AJ3" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1213,64 +1213,64 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AY3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA3" t="n">
         <v>4.7</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 11:20:18</t>
+          <t>2026-07-06 13:27:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB3"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,493 +848,747 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>1.86</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.11</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.51</v>
-      </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2</v>
+        <v>1.11</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 13:27:40</t>
+          <t>2026-07-06 15:34:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Operario PR</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-07-06 15:34:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Ecuadorian Serie A</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>21:00:00</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Aucas</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Guayaquil City</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.58</v>
       </c>
-      <c r="H3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>10.5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>4.1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" t="n">
         <v>4.9</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>1.32</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" t="n">
         <v>1.06</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N4" t="n">
         <v>3.55</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O4" t="n">
         <v>1.31</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P4" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" t="n">
         <v>1.94</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R4" t="n">
         <v>1.3</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S4" t="n">
         <v>3.6</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" t="n">
         <v>2.08</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>1.75</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V4" t="n">
         <v>1.11</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W4" t="n">
         <v>2.72</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X4" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y4" t="n">
         <v>28</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z4" t="n">
         <v>95</v>
       </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC4" t="n">
         <v>970</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD4" t="n">
         <v>32</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE4" t="n">
         <v>190</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF4" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG4" t="n">
         <v>12</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH4" t="n">
         <v>36</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI4" t="n">
         <v>160</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ4" t="n">
         <v>16</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK4" t="n">
         <v>23</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL4" t="n">
         <v>55</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
         <v>11</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AQ4" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AR4" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AS4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AT4" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AU4" t="n">
         <v>3.35</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AV4" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AX4" t="n">
         <v>3.25</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AY4" t="n">
         <v>3.45</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ4" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BA4" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB4" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BC4" t="n">
         <v>4</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BD4" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BE4" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BF4" t="n">
         <v>3.4</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BG4" t="n">
         <v>4.8</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BH4" t="n">
         <v>3.6</v>
       </c>
-      <c r="BI3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
+      <c r="BI4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
         <v>6</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>11</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BN4" t="n">
         <v>4</v>
       </c>
-      <c r="BO3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ3" t="n">
+      <c r="BO4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>5.4</v>
       </c>
-      <c r="BR3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS3" t="n">
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
         <v>5.8</v>
       </c>
-      <c r="BV3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW3" t="n">
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
         <v>10</v>
       </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>10</v>
       </c>
-      <c r="BZ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-06 13:27:40</t>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-07-06 15:34:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -875,19 +875,19 @@
         <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
         <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
         <v>1.11</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 15:34:52</t>
+          <t>2026-07-06 17:41:39</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
         <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.49</v>
@@ -1147,7 +1147,7 @@
         <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
         <v>5.2</v>
@@ -1159,10 +1159,10 @@
         <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 15:34:52</t>
+          <t>2026-07-06 17:41:39</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
         <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1449,7 +1449,7 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>160</v>
@@ -1458,7 +1458,7 @@
         <v>16</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1467,7 +1467,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1476,58 +1476,58 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT4" t="n">
         <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI4" t="n">
         <v>2.8</v>
@@ -1536,16 +1536,16 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO4" t="n">
         <v>3.45</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 15:34:52</t>
+          <t>2026-07-06 17:41:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,52 +857,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -911,166 +911,166 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -1144,22 +1144,22 @@
         <v>1.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
         <v>5.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
         <v>1.59</v>
@@ -1174,19 +1174,19 @@
         <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>16</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.4</v>
@@ -1228,10 +1228,10 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1252,25 +1252,25 @@
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8</v>
       </c>
-      <c r="BE3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH3" t="n">
         <v>2.84</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.8</v>
@@ -1389,7 +1389,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
@@ -1401,31 +1401,31 @@
         <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
         <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1437,25 +1437,25 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AE4" t="n">
         <v>190</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AI4" t="n">
         <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
@@ -1476,55 +1476,55 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT4" t="n">
         <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB4" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="BC4" t="n">
         <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.55</v>
@@ -1560,7 +1560,7 @@
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 17:41:39</t>
+          <t>2026-07-06 19:48:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -860,16 +860,16 @@
         <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
@@ -890,10 +890,10 @@
         <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
         <v>2.04</v>
@@ -902,7 +902,7 @@
         <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -911,10 +911,10 @@
         <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -923,100 +923,100 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>55</v>
       </c>
       <c r="AF2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>19</v>
-      </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM2" t="n">
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO2" t="n">
         <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY2" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 19:48:01</t>
+          <t>2026-07-06 21:54:08</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G3" t="n">
         <v>2.68</v>
@@ -1123,7 +1123,7 @@
         <v>3.55</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
         <v>3.15</v>
@@ -1135,7 +1135,7 @@
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.52</v>
@@ -1210,7 +1210,7 @@
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN3" t="n">
         <v>42</v>
@@ -1240,40 +1240,40 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI3" t="n">
         <v>2.32</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>5.4</v>
@@ -1300,13 +1300,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT3" t="n">
         <v>6.6</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 19:48:01</t>
+          <t>2026-07-06 21:54:08</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>1.52</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>10.5</v>
@@ -1389,7 +1389,7 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
@@ -1413,7 +1413,7 @@
         <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
         <v>2.92</v>
@@ -1431,7 +1431,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1443,7 +1443,7 @@
         <v>190</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
@@ -1461,7 +1461,7 @@
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1476,13 +1476,13 @@
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="AT4" t="n">
         <v>5.6</v>
@@ -1491,61 +1491,61 @@
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>2.78</v>
       </c>
       <c r="AX4" t="n">
         <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="BF4" t="n">
         <v>7</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="BH4" t="n">
         <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BO4" t="n">
         <v>3.45</v>
@@ -1554,31 +1554,31 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 19:48:01</t>
+          <t>2026-07-06 21:54:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -860,19 +860,19 @@
         <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.21</v>
@@ -881,19 +881,19 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
         <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>2.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S2" t="n">
         <v>2.04</v>
@@ -902,7 +902,7 @@
         <v>1.51</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -941,13 +941,13 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>44</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>16.5</v>
@@ -965,58 +965,58 @@
         <v>36</v>
       </c>
       <c r="AP2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS2" t="n">
+      <c r="BE2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BF2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG2" t="n">
         <v>7</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-06 21:54:08</t>
+          <t>2026-07-07 00:00:04</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>3.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.15</v>
@@ -1147,7 +1147,7 @@
         <v>2.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
         <v>5.2</v>
@@ -1156,13 +1156,13 @@
         <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.4</v>
@@ -1228,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1240,37 +1240,37 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="n">
         <v>2.82</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-06 21:54:08</t>
+          <t>2026-07-07 00:00:04</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1389,46 +1389,46 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
         <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
         <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="n">
         <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB4" t="n">
         <v>7</v>
@@ -1437,19 +1437,19 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AE4" t="n">
         <v>190</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>160</v>
@@ -1467,64 +1467,64 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.78</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.78</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.78</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="n">
         <v>3.55</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.5</v>
+        <v>2.38</v>
       </c>
       <c r="BN4" t="n">
         <v>3.9</v>
@@ -1566,7 +1566,7 @@
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-06 21:54:08</t>
+          <t>2026-07-07 00:00:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
         <v>5.2</v>
@@ -872,37 +872,37 @@
         <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R2" t="n">
         <v>1.78</v>
       </c>
       <c r="S2" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -917,7 +917,7 @@
         <v>30</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
         <v>110</v>
@@ -932,7 +932,7 @@
         <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>15.5</v>
@@ -956,70 +956,70 @@
         <v>25</v>
       </c>
       <c r="AM2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR2" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>3.65</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BI2" t="n">
         <v>3.4</v>
@@ -1028,13 +1028,13 @@
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="BN2" t="n">
         <v>5.2</v>
@@ -1046,31 +1046,31 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="BT2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00:04</t>
+          <t>2026-07-07 02:06:19</t>
         </is>
       </c>
     </row>
@@ -1114,55 +1114,55 @@
         <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
         <v>1.12</v>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
         <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1228,7 +1228,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.4</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX3" t="n">
         <v>11.5</v>
@@ -1252,7 +1252,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
@@ -1261,16 +1261,16 @@
         <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3" t="n">
         <v>2.82</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00:04</t>
+          <t>2026-07-07 02:06:19</t>
         </is>
       </c>
     </row>
@@ -1365,73 +1365,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
         <v>370</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1449,7 +1449,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
         <v>160</v>
@@ -1461,40 +1461,40 @@
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO4" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AT4" t="n">
         <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1503,64 +1503,64 @@
         <v>8.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD4" t="n">
         <v>8</v>
       </c>
-      <c r="BB4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BF4" t="n">
         <v>7.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO4" t="n">
         <v>3.45</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 00:00:04</t>
+          <t>2026-07-07 02:06:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,220 +857,220 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K2" t="n">
         <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
         <v>30</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF2" t="n">
         <v>13</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
         <v>21</v>
       </c>
-      <c r="AE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR2" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
@@ -1132,13 +1132,13 @@
         <v>1.57</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3" t="n">
         <v>1.56</v>
@@ -1150,31 +1150,31 @@
         <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
         <v>9.4</v>
@@ -1210,40 +1210,40 @@
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
         <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
@@ -1261,22 +1261,22 @@
         <v>8.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="n">
         <v>2.82</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ3" t="n">
         <v>11.5</v>
@@ -1288,28 +1288,28 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>5.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
         <v>5.5</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AA4" t="n">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE4" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX4" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>6</v>
       </c>
-      <c r="AU4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 02:06:19</t>
+          <t>2026-07-07 04:12:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,73 +857,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H2" t="n">
         <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
         <v>5.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
         <v>150</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
@@ -932,16 +932,16 @@
         <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
@@ -953,40 +953,40 @@
         <v>17.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
         <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
         <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.6</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,31 +998,31 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2" t="n">
         <v>9.800000000000001</v>
@@ -1043,10 +1043,10 @@
         <v>3.7</v>
       </c>
       <c r="BP2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
         <v>21</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 04:12:23</t>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
@@ -1129,28 +1129,28 @@
         <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
         <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q3" t="n">
         <v>2.72</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T3" t="n">
         <v>2.08</v>
@@ -1162,7 +1162,7 @@
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X3" t="n">
         <v>9</v>
@@ -1177,10 +1177,10 @@
         <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1204,22 +1204,22 @@
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO3" t="n">
         <v>75</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.2</v>
@@ -1240,31 +1240,31 @@
         <v>6.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE3" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 04:12:23</t>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
@@ -1380,7 +1380,7 @@
         <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1392,19 +1392,19 @@
         <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.98</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.94</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
         <v>2.22</v>
@@ -1419,7 +1419,7 @@
         <v>3.15</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>28</v>
@@ -1461,7 +1461,7 @@
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
         <v>230</v>
@@ -1479,7 +1479,7 @@
         <v>5.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS4" t="n">
         <v>3.7</v>
@@ -1494,7 +1494,7 @@
         <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4" t="n">
         <v>6.8</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 04:12:23</t>
+          <t>2026-07-07 06:18:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,175 +857,175 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="G2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
         <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
         <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
         <v>4.9</v>
@@ -1037,40 +1037,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BO2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5</v>
-      </c>
       <c r="BR2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
         <v>2.98</v>
@@ -1129,64 +1129,64 @@
         <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z3" t="n">
         <v>24</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
         <v>16</v>
@@ -1195,10 +1195,10 @@
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
@@ -1207,40 +1207,40 @@
         <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1249,37 +1249,37 @@
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>48</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
         <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3" t="n">
         <v>8.6</v>
@@ -1288,16 +1288,16 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ3" t="n">
         <v>8.199999999999999</v>
@@ -1306,10 +1306,10 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU3" t="n">
         <v>5.5</v>
@@ -1324,7 +1324,7 @@
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
         <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1389,22 +1389,22 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.94</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.98</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
         <v>2.22</v>
@@ -1413,7 +1413,7 @@
         <v>1.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
         <v>3.15</v>
@@ -1422,7 +1422,7 @@
         <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
@@ -1473,7 +1473,7 @@
         <v>350</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ4" t="n">
         <v>5.6</v>
@@ -1482,7 +1482,7 @@
         <v>6.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1494,7 +1494,7 @@
         <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX4" t="n">
         <v>6.8</v>
@@ -1503,28 +1503,28 @@
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>3.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 06:18:40</t>
+          <t>2026-07-07 08:01:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -887,34 +887,34 @@
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
         <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U2" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="X2" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y2" t="n">
         <v>34</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>38</v>
       </c>
       <c r="Z2" t="n">
         <v>70</v>
@@ -923,70 +923,70 @@
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>95</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV2" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -995,13 +995,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC2" t="n">
         <v>12.5</v>
@@ -1010,13 +1010,13 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="BF2" t="n">
         <v>4.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="n">
         <v>5.1</v>
@@ -1025,10 +1025,10 @@
         <v>3.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1037,16 +1037,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BN2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>4.8</v>
       </c>
       <c r="BR2" t="n">
         <v>19.5</v>
@@ -1055,22 +1055,22 @@
         <v>6.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BW2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1111,100 +1111,100 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H3" t="n">
         <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
         <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
@@ -1213,67 +1213,67 @@
         <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AO3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BB3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI3" t="n">
         <v>2.24</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1306,7 +1306,7 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>6.6</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
@@ -1380,7 +1380,7 @@
         <v>4.6</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1401,28 +1401,28 @@
         <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
         <v>110</v>
@@ -1431,58 +1431,58 @@
         <v>460</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE4" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
         <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>350</v>
+        <v>430</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>6.4</v>
@@ -1491,22 +1491,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1518,77 +1518,77 @@
         <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>12.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BO4" t="n">
         <v>3.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 08:01:34</t>
+          <t>2026-07-07 10:07:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G2" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -881,34 +881,34 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
         <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -917,64 +917,64 @@
         <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>15</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>14.5</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -983,94 +983,94 @@
         <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>7.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
         <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP2" t="n">
         <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.62</v>
@@ -1135,13 +1135,13 @@
         <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>1.59</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q3" t="n">
         <v>2.86</v>
@@ -1153,19 +1153,19 @@
         <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
         <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
@@ -1174,7 +1174,7 @@
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB3" t="n">
         <v>7.6</v>
@@ -1183,19 +1183,19 @@
         <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
         <v>14</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>100</v>
@@ -1204,34 +1204,34 @@
         <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AN3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO3" t="n">
         <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1255,7 +1255,7 @@
         <v>60</v>
       </c>
       <c r="BB3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BC3" t="n">
         <v>34</v>
@@ -1264,13 +1264,13 @@
         <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
         <v>2.7</v>
@@ -1282,7 +1282,7 @@
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
@@ -1294,10 +1294,10 @@
         <v>5.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
         <v>8.199999999999999</v>
@@ -1315,7 +1315,7 @@
         <v>5.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
         <v>9.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
         <v>1.45</v>
       </c>
       <c r="H4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
         <v>4.6</v>
@@ -1383,34 +1383,34 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
@@ -1422,25 +1422,25 @@
         <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA4" t="n">
-        <v>460</v>
+        <v>610</v>
       </c>
       <c r="AB4" t="n">
         <v>8</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>44</v>
       </c>
       <c r="AE4" t="n">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="AF4" t="n">
         <v>8.800000000000001</v>
@@ -1452,143 +1452,143 @@
         <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AJ4" t="n">
         <v>13.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>430</v>
+        <v>530</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>55</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
         <v>24</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF4" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BP4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 10:07:56</t>
+          <t>2026-07-07 12:14:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H2" t="n">
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
         <v>4.9</v>
@@ -881,19 +881,19 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
         <v>1.49</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
         <v>2.2</v>
@@ -908,10 +908,10 @@
         <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Y2" t="n">
         <v>34</v>
@@ -920,13 +920,13 @@
         <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
         <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
         <v>26</v>
@@ -935,16 +935,16 @@
         <v>130</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
         <v>15</v>
@@ -956,25 +956,25 @@
         <v>28</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
         <v>5.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -986,7 +986,7 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -998,25 +998,25 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>5</v>
@@ -1040,7 +1040,7 @@
         <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>9</v>
@@ -1052,7 +1052,7 @@
         <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
@@ -1061,7 +1061,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BV2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW2" t="n">
         <v>9.199999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
         <v>2.66</v>
@@ -1120,16 +1120,16 @@
         <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
@@ -1144,7 +1144,7 @@
         <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1153,7 +1153,7 @@
         <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
         <v>1.78</v>
@@ -1177,22 +1177,22 @@
         <v>85</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -1207,7 +1207,7 @@
         <v>48</v>
       </c>
       <c r="AL3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM3" t="n">
         <v>220</v>
@@ -1216,13 +1216,13 @@
         <v>70</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
         <v>18.5</v>
@@ -1231,7 +1231,7 @@
         <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
         <v>13</v>
@@ -1264,13 +1264,13 @@
         <v>46</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BH3" t="n">
         <v>2.7</v>
@@ -1300,7 +1300,7 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1330,11 +1330,11 @@
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
@@ -1389,28 +1389,28 @@
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
@@ -1419,46 +1419,46 @@
         <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE4" t="n">
         <v>300</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI4" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
@@ -1467,85 +1467,85 @@
         <v>330</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
         <v>530</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BO4" t="n">
         <v>3.3</v>
@@ -1557,10 +1557,10 @@
         <v>5.8</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4" t="n">
         <v>13.5</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>14.5</v>
+        <v>1.56</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 12:14:32</t>
+          <t>2026-07-07 14:21:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G2" t="n">
         <v>1.56</v>
@@ -866,13 +866,13 @@
         <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.25</v>
@@ -881,43 +881,43 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
         <v>2.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
         <v>2.78</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y2" t="n">
         <v>34</v>
       </c>
       <c r="Z2" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AA2" t="n">
         <v>170</v>
@@ -932,7 +932,7 @@
         <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -947,13 +947,13 @@
         <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM2" t="n">
         <v>110</v>
@@ -962,31 +962,31 @@
         <v>5.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="AR2" t="n">
         <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
@@ -995,19 +995,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE2" t="n">
         <v>23</v>
@@ -1016,7 +1016,7 @@
         <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="n">
         <v>5</v>
@@ -1025,16 +1025,16 @@
         <v>4</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2" t="n">
         <v>4.7</v>
@@ -1046,13 +1046,13 @@
         <v>9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>19</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT2" t="n">
         <v>11</v>
@@ -1064,13 +1064,13 @@
         <v>46</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G3" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="H3" t="n">
         <v>3.35</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
         <v>1.63</v>
@@ -1138,13 +1138,13 @@
         <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
         <v>1.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1153,7 +1153,7 @@
         <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U3" t="n">
         <v>1.78</v>
@@ -1162,76 +1162,76 @@
         <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z3" t="n">
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
         <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
         <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
         <v>80</v>
       </c>
       <c r="AM3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN3" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AP3" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
         <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>6.4</v>
@@ -1240,13 +1240,13 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
@@ -1261,19 +1261,19 @@
         <v>34</v>
       </c>
       <c r="BD3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BE3" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG3" t="n">
-        <v>65</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI3" t="n">
         <v>2.24</v>
@@ -1282,13 +1282,13 @@
         <v>12</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
         <v>5.3</v>
@@ -1297,19 +1297,19 @@
         <v>4.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU3" t="n">
         <v>5.5</v>
@@ -1318,23 +1318,23 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1374,16 @@
         <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1395,28 +1395,28 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
@@ -1425,10 +1425,10 @@
         <v>29</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB4" t="n">
         <v>6.6</v>
@@ -1440,16 +1440,16 @@
         <v>42</v>
       </c>
       <c r="AE4" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1464,25 +1464,25 @@
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="AN4" t="n">
         <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1494,7 +1494,7 @@
         <v>36</v>
       </c>
       <c r="AW4" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1506,25 +1506,25 @@
         <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BF4" t="n">
         <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.35</v>
@@ -1548,7 +1548,7 @@
         <v>3.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP4" t="n">
         <v>8.800000000000001</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 14:21:10</t>
+          <t>2026-07-07 16:27:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -857,85 +857,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>6.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="P2" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
         <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="X2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z2" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA2" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
         <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -947,61 +947,61 @@
         <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK2" t="n">
         <v>15</v>
       </c>
       <c r="AL2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>27</v>
       </c>
-      <c r="AM2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
         <v>10.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -1010,67 +1010,67 @@
         <v>21</v>
       </c>
       <c r="BE2" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BG2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4</v>
-      </c>
       <c r="BJ2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>11</v>
-      </c>
       <c r="BU2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BV2" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="BX2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1114,37 +1114,37 @@
         <v>2.64</v>
       </c>
       <c r="G3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I3" t="n">
         <v>3.35</v>
       </c>
-      <c r="I3" t="n">
-        <v>3.45</v>
-      </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O3" t="n">
         <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
@@ -1159,7 +1159,7 @@
         <v>1.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
         <v>1.58</v>
@@ -1168,73 +1168,73 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
         <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3" t="n">
         <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
         <v>85</v>
       </c>
       <c r="AJ3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK3" t="n">
         <v>42</v>
       </c>
-      <c r="AK3" t="n">
-        <v>40</v>
-      </c>
       <c r="AL3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>75</v>
+        <v>970</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT3" t="n">
         <v>7</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
         <v>14</v>
@@ -1246,95 +1246,95 @@
         <v>13.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC3" t="n">
         <v>36</v>
       </c>
-      <c r="BC3" t="n">
-        <v>34</v>
-      </c>
       <c r="BD3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BG3" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP3" t="n">
         <v>26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA3" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
         <v>1.44</v>
@@ -1374,13 +1374,13 @@
         <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.44</v>
@@ -1395,22 +1395,22 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
@@ -1431,46 +1431,46 @@
         <v>520</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
         <v>42</v>
       </c>
       <c r="AE4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
         <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN4" t="n">
         <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1479,10 +1479,10 @@
         <v>28</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1491,10 +1491,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1506,43 +1506,43 @@
         <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
         <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>13.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN4" t="n">
         <v>3.6</v>
@@ -1554,41 +1554,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR4" t="n">
         <v>32</v>
       </c>
       <c r="BS4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BU4" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.56</v>
+        <v>14.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 16:27:59</t>
+          <t>2026-07-07 18:34:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,246 +848,246 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Operario PR</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>2.98</v>
       </c>
       <c r="H2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="R2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="S2" t="n">
+        <v>23</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y2" t="n">
         <v>6.8</v>
       </c>
-      <c r="J2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
         <v>5.7</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X2" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>840</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>200</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>160</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="BO2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>330</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT2" t="n">
         <v>13</v>
       </c>
-      <c r="AU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BU2" t="n">
         <v>7.4</v>
       </c>
-      <c r="BL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BV2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,244 +1097,244 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="G3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>510</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>550</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR3" t="n">
         <v>2.7</v>
       </c>
-      <c r="H3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="AS3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>3.35</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="BA3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>9</v>
       </c>
-      <c r="Z3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="BR3" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU3" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BV3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BW3" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>65</v>
       </c>
       <c r="BY3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>
@@ -1365,94 +1365,94 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="n">
         <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC4" t="n">
         <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="n">
         <v>250</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ4" t="n">
         <v>11.5</v>
@@ -1461,28 +1461,28 @@
         <v>17.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>490</v>
+        <v>390</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>260</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1491,22 +1491,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1515,80 +1515,80 @@
         <v>15.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BE4" t="n">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>15.5</v>
+        <v>180</v>
       </c>
       <c r="BN4" t="n">
         <v>3.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS4" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-07-07 18:34:43</t>
+          <t>2026-07-07 20:41:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,114 +843,114 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Operario PR</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>1.15</v>
       </c>
       <c r="G2" t="n">
-        <v>2.98</v>
+        <v>1.18</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>65</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="J2" t="n">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="K2" t="n">
-        <v>2.46</v>
+        <v>8.6</v>
       </c>
       <c r="L2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="O2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="P2" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="T2" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="X2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AH2" t="n">
-        <v>840</v>
+        <v>350</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AL2" t="n">
         <v>1000</v>
@@ -959,636 +959,128 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.9</v>
+        <v>50</v>
       </c>
       <c r="AR2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY2" t="n">
         <v>20</v>
       </c>
-      <c r="AS2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>260</v>
+      </c>
+      <c r="BB2" t="n">
         <v>24</v>
       </c>
-      <c r="AW2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>200</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>55</v>
-      </c>
       <c r="BC2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="BD2" t="n">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BG2" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-07-07 20:41:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CD Gualberto Villarroel</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="X3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>510</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>550</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>180</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-07-07 20:41:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ecuadorian Serie A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Aucas</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Guayaquil City</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>490</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>280</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>390</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>260</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>180</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>29</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-07-07 20:41:22</t>
+          <t>2026-07-07 22:47:48</t>
         </is>
       </c>
     </row>
